--- a/Ozrit HR data/ozrit/Daily updates for hr_.xlsx
+++ b/Ozrit HR data/ozrit/Daily updates for hr_.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixld\Downloads\ozrit\Ozrit HR data\ozrit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F99963-657A-4798-AE96-22DAF4B91F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D49D38C-E7A8-4194-B894-0DD5AF5E65F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="624">
   <si>
     <t xml:space="preserve">Date </t>
   </si>
@@ -1943,6 +1943,12 @@
   </si>
   <si>
     <t xml:space="preserve">posted internship for HR </t>
+  </si>
+  <si>
+    <t>09.09.2025</t>
+  </si>
+  <si>
+    <t>ATS research</t>
   </si>
 </sst>
 </file>
@@ -4418,6 +4424,12 @@
       <c r="E233" s="2"/>
     </row>
     <row r="234" spans="1:5" ht="12.5">
+      <c r="A234" t="s">
+        <v>622</v>
+      </c>
+      <c r="C234" s="95" t="s">
+        <v>623</v>
+      </c>
       <c r="E234" s="2"/>
     </row>
     <row r="235" spans="1:5" ht="12.5">
